--- a/tests/fixtures/03_purchase_order/pattern.xlsx
+++ b/tests/fixtures/03_purchase_order/pattern.xlsx
@@ -453,12 +453,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lbl.po</t>
+          <t>po_label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,12 +475,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>po.number</t>
+          <t>date_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -490,19 +490,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PO-[0-9]{4}</t>
+          <t>Date:</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lbl.date</t>
+          <t>vendor_label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -512,41 +512,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Vendor:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>po.date</t>
+          <t>ref_label</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>Ref:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lbl.vendor</t>
+          <t>col_item</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -556,19 +556,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vendor:</t>
+          <t>Item</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vendor.name</t>
+          <t>col_desc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -578,19 +578,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lbl.ref</t>
+          <t>col_qty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -600,19 +600,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ref:</t>
+          <t>Qty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vendor.ref</t>
+          <t>col_price</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[A-Z0-9]+</t>
+          <t>Unit Price</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>col.item</t>
+          <t>col_total</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -644,19 +644,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>col.desc</t>
+          <t>po.number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,41 +666,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>PO-[0-9]{4}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>col.qty</t>
+          <t>po.date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>col.price</t>
+          <t>vendor.name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -710,19 +710,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>.+</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>col.total</t>
+          <t>vendor.ref</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>[A-Z0-9]+</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lbl.po</t>
+          <t>po_label</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lbl.date</t>
+          <t>date_label</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>lbl.vendor</t>
+          <t>vendor_label</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lbl.ref</t>
+          <t>ref_label</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>col.item</t>
+          <t>col_item</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>col.desc</t>
+          <t>col_desc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>col.qty</t>
+          <t>col_qty</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>col.price</t>
+          <t>col_price</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>col.total</t>
+          <t>col_total</t>
         </is>
       </c>
     </row>
